--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486462_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486462_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.0383</v>
+        <v>11.5316</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0383</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9999</v>
+        <v>1.5992</v>
       </c>
       <c r="G2" t="n">
         <v>5.4036</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0273</v>
+        <v>0.5206</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1644</v>
+        <v>-0.2704</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1917</v>
+        <v>0.791</v>
       </c>
       <c r="V2" t="n">
         <v>4.5199</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.4438</v>
+        <v>8.382099999999999</v>
       </c>
       <c r="E3" t="n">
         <v>6.613</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8308</v>
+        <v>1.7691</v>
       </c>
       <c r="G3" t="n">
         <v>3.8052</v>
@@ -688,13 +688,13 @@
         <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1834</v>
+        <v>1.1218</v>
       </c>
       <c r="T3" t="n">
         <v>0.2572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9263</v>
+        <v>0.8646</v>
       </c>
       <c r="V3" t="n">
         <v>3.0202</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0234</v>
+        <v>3.6592</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4487</v>
+        <v>4.3312</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4254</v>
+        <v>-0.672</v>
       </c>
       <c r="G4" t="n">
         <v>2.0501</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1032</v>
+        <v>0.739</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3447</v>
+        <v>0.2271</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7585</v>
+        <v>0.5119</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0385</v>
+        <v>0.331</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2022</v>
+        <v>-0.1936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1637</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8623</v>
+        <v>-1.1376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4653</v>
+        <v>-1.4842</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3276</v>
+        <v>0.3466</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2279</v>
+        <v>-0.3334</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9307</v>
+        <v>-0.4864</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1587</v>
+        <v>0.153</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6344</v>
+        <v>-0.8042</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4654</v>
+        <v>-0.9978</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1689</v>
+        <v>0.1936</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6286</v>
+        <v>0.7291</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2656</v>
+        <v>0.0973</v>
       </c>
       <c r="U5" t="n">
-        <v>0.363</v>
+        <v>0.6318</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7602</v>
+        <v>0.7395</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2286</v>
+        <v>0.2489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0462</v>
+        <v>-0.5564</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2748</v>
+        <v>0.8053</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.542</v>
+        <v>-2.0901</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3467</v>
+        <v>0.4407</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1952</v>
+        <v>-2.5308</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0565</v>
+        <v>-0.438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0182</v>
+        <v>1.6059</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>-2.0439</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5985</v>
+        <v>-1.6521</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.365</v>
+        <v>-1.1652</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2335</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>2.3926</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0959</v>
+        <v>-0.2488</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2055</v>
+        <v>-0.3136</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3014</v>
+        <v>0.0649</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
         <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4821</v>
+        <v>-0.1785</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9759</v>
+        <v>0.158</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4938</v>
+        <v>-0.3364</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1376</v>
+        <v>-0.542</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4842</v>
+        <v>-0.3467</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3466</v>
+        <v>-0.1952</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3334</v>
+        <v>0.0565</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4864</v>
+        <v>0.0182</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>0.0382</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8042</v>
+        <v>-0.5985</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9978</v>
+        <v>-0.365</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1936</v>
+        <v>-0.2335</v>
       </c>
       <c r="P7" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.146</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.601</v>
+        <v>0.2397</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9033</v>
+        <v>-0.2312</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3387</v>
+        <v>-0.4257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4354</v>
+        <v>0.1945</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0901</v>
+        <v>-1.8623</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4407</v>
+        <v>0.4653</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5308</v>
+        <v>-2.3276</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.438</v>
+        <v>-1.2279</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6059</v>
+        <v>0.9307</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0439</v>
+        <v>-2.1587</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6521</v>
+        <v>-0.6344</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1652</v>
+        <v>-0.4654</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4869</v>
+        <v>-0.1689</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4009</v>
+        <v>0.4359</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0959</v>
+        <v>0.0421</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.305</v>
+        <v>0.3939</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2205</v>
+        <v>-1.5536</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4183</v>
+        <v>-1.5524</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6388</v>
+        <v>-0.0013</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3116</v>
+        <v>-1.5158</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6327</v>
+        <v>-0.213</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-1.3028</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7007</v>
+        <v>-1.4154</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0616</v>
+        <v>0.0365</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3609</v>
+        <v>-1.4519</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0123</v>
+        <v>-0.1004</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6943</v>
+        <v>-0.2495</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.318</v>
+        <v>0.149</v>
       </c>
       <c r="P9" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6338</v>
+        <v>-0.2346</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8051</v>
+        <v>-0.137</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1714</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7602</v>
+        <v>-0.0207</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7602</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5844</v>
+        <v>-1.656</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5524</v>
+        <v>-0.1405</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0321</v>
+        <v>-1.5155</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5158</v>
+        <v>-1.3116</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.213</v>
+        <v>-0.6327</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3028</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4154</v>
+        <v>0.7007</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0365</v>
+        <v>1.0616</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4519</v>
+        <v>-0.3609</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1004</v>
+        <v>-2.0123</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2495</v>
+        <v>-1.6943</v>
       </c>
       <c r="O10" t="n">
-        <v>0.149</v>
+        <v>-0.318</v>
       </c>
       <c r="P10" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2655</v>
+        <v>0.1983</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.137</v>
+        <v>0.2464</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1285</v>
+        <v>-0.0481</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0207</v>
+        <v>-0.7602</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0207</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7794</v>
+        <v>-2.1744</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4082</v>
+        <v>-6.0332</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3713</v>
+        <v>3.8588</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2081</v>
+        <v>-4.7192</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3194</v>
+        <v>-0.8609</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5275</v>
+        <v>-3.8583</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0382</v>
+        <v>-4.927</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5538</v>
+        <v>-0.3436</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5921</v>
+        <v>-4.5835</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1698</v>
+        <v>0.2078</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2344</v>
+        <v>-0.5173</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0645</v>
+        <v>0.7251</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3411</v>
+        <v>0.6748</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8051</v>
+        <v>-0.2139</v>
       </c>
       <c r="U11" t="n">
-        <v>0.536</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2599</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3594</v>
+        <v>-2.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0332</v>
+        <v>-2.0787</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6738</v>
+        <v>-0.3713</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.7192</v>
+        <v>-0.2081</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8609</v>
+        <v>0.3194</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8583</v>
+        <v>-0.5275</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.927</v>
+        <v>-0.0382</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3436</v>
+        <v>0.5538</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.5835</v>
+        <v>-0.5921</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2078</v>
+        <v>-0.1698</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5173</v>
+        <v>-0.2344</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7251</v>
+        <v>0.0645</v>
       </c>
       <c r="P12" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4898</v>
+        <v>0.6705</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2139</v>
+        <v>0.1346</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7037</v>
+        <v>0.536</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="13">
@@ -1423,55 +1423,55 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.9093</v>
+        <v>15.9091</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0539</v>
+        <v>10.0541</v>
       </c>
       <c r="F13" t="n">
-        <v>5.855</v>
+        <v>5.8551</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1278</v>
+        <v>-2.127800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.888199999999999</v>
+        <v>2.8882</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.015899999999999</v>
+        <v>-5.015899999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>6.069700000000001</v>
+        <v>6.069699999999999</v>
       </c>
       <c r="K13" t="n">
         <v>11.2088</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.1396</v>
+        <v>-5.139600000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-8.1973</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.3207</v>
+        <v>-8.320700000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1232</v>
+        <v>0.1231999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>6.525099999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.787699999999999</v>
+        <v>-9.787700000000001</v>
       </c>
       <c r="R13" t="n">
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7527</v>
+        <v>4.7526</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.02400000000000027</v>
+        <v>-0.02389999999999995</v>
       </c>
       <c r="U13" t="n">
         <v>4.7767</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3178</v>
+        <v>1.6088</v>
       </c>
       <c r="E14" t="n">
         <v>2.5057</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1879</v>
+        <v>-0.8969</v>
       </c>
       <c r="G14" t="n">
         <v>1.6325</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4503</v>
+        <v>-0.2587</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2824</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7327</v>
+        <v>0.0237</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8525</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.075</v>
+        <v>0.5262</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.083</v>
+        <v>-0.636</v>
       </c>
       <c r="F15" t="n">
-        <v>1.008</v>
+        <v>1.1621</v>
       </c>
       <c r="G15" t="n">
         <v>0.5384</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9163</v>
+        <v>-0.3151</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.5119</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0427</v>
+        <v>0.1968</v>
       </c>
       <c r="V15" t="n">
         <v>0.9554</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5085</v>
+        <v>-0.3313</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0194</v>
+        <v>1.7959</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5279</v>
+        <v>-2.1272</v>
       </c>
       <c r="G16" t="n">
         <v>3.0771</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4933</v>
+        <v>-1.3162</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7619</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7315</v>
+        <v>-0.3308</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2223</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.016</v>
+        <v>-1.3336</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1171</v>
+        <v>-0.9333</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8989</v>
+        <v>-0.4004</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.287</v>
+        <v>0.2311</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9396</v>
+        <v>-0.0852</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6526</v>
+        <v>0.3163</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8502</v>
+        <v>0.385</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3713</v>
+        <v>0.3467</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4789</v>
+        <v>0.0382</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1372</v>
+        <v>-0.1539</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3109</v>
+        <v>-0.432</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1737</v>
+        <v>0.2781</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3787</v>
+        <v>0.0655</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1202</v>
+        <v>-0.2307</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2585</v>
+        <v>0.2962</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3252</v>
+        <v>-0.7602</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3252</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.507</v>
+        <v>-1.4837</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.045</v>
+        <v>-1.4451</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.462</v>
+        <v>-0.0386</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2311</v>
+        <v>-0.6829</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0852</v>
+        <v>0.0638</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3163</v>
+        <v>-0.7467</v>
       </c>
       <c r="J18" t="n">
-        <v>0.385</v>
+        <v>-0.3751</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3467</v>
+        <v>1.0767</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>-1.4519</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1539</v>
+        <v>-0.3077</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.432</v>
+        <v>-1.0129</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2781</v>
+        <v>0.7052</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1079</v>
+        <v>-0.6708</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3425</v>
+        <v>-0.7426</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2346</v>
+        <v>0.0718</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5703</v>
+        <v>-1.6558</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8966</v>
+        <v>-0.7877</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4669</v>
+        <v>-0.8681</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1496</v>
+        <v>-0.287</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5413</v>
+        <v>-0.9396</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6909</v>
+        <v>0.6526</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.8502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9371</v>
+        <v>0.3713</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2279</v>
+        <v>0.4789</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5596</v>
+        <v>-1.1372</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4783</v>
+        <v>-1.3109</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9187</v>
+        <v>0.1737</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3443</v>
+        <v>-0.2611</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0601</v>
+        <v>-0.5504</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4044</v>
+        <v>0.2893</v>
       </c>
       <c r="V19" t="n">
-        <v>1.017</v>
+        <v>-1.3252</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3729</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4432</v>
+        <v>-1.7515</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0039</v>
+        <v>0.5613</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4393</v>
+        <v>-2.3128</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6829</v>
+        <v>0.1496</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0638</v>
+        <v>-0.5413</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7467</v>
+        <v>0.6909</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3751</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0767</v>
+        <v>0.9371</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4519</v>
+        <v>-0.2279</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3077</v>
+        <v>-0.5596</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0129</v>
+        <v>-1.4783</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7052</v>
+        <v>0.9187</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6303</v>
+        <v>-0.5254</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3014</v>
+        <v>-0.2752</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3289</v>
+        <v>-0.2503</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7602</v>
+        <v>3.3899</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5396</v>
+        <v>-2.5897</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5429</v>
+        <v>-2.6546</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0033</v>
+        <v>0.0649</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2503</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.122</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9462</v>
+        <v>-4.3745</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6389</v>
+        <v>-2.846</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3073</v>
+        <v>-1.5286</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8555</v>
+        <v>0.5748</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2617</v>
+        <v>-1.183</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1172</v>
+        <v>1.7579</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9278999999999999</v>
+        <v>0.9646</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1925</v>
+        <v>-0.8331</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1204</v>
+        <v>1.7977</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0723</v>
+        <v>-0.3898</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.3499</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0032</v>
+        <v>-0.0399</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.26</v>
+        <v>-1.0311</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.548</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0135</v>
+        <v>-0.4831</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1332</v>
+        <v>-0.8732</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.2631</v>
+        <v>-0.8732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6211</v>
+        <v>-4.524</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.846</v>
+        <v>-1.4154</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7751</v>
+        <v>-3.1087</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5748</v>
+        <v>-0.8555</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.183</v>
+        <v>0.2617</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7579</v>
+        <v>-1.1172</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9646</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8331</v>
+        <v>1.1925</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7977</v>
+        <v>-2.1204</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3898</v>
+        <v>0.0723</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3499</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0399</v>
+        <v>1.0032</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0451</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2776</v>
+        <v>-0.3179</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.5299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7297</v>
+        <v>0.2121</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8732</v>
+        <v>-3.1332</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8732</v>
+        <v>-4.2631</v>
       </c>
     </row>
     <row r="24">
@@ -2284,25 +2284,25 @@
         <v>-15.9091</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.855099999999998</v>
+        <v>-5.8552</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.054</v>
+        <v>-10.0543</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1278</v>
+        <v>2.127800000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-2.8881</v>
       </c>
       <c r="I24" t="n">
-        <v>5.016100000000001</v>
+        <v>5.0161</v>
       </c>
       <c r="J24" t="n">
-        <v>8.1975</v>
+        <v>8.197500000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>8.3208</v>
+        <v>8.320799999999998</v>
       </c>
       <c r="L24" t="n">
         <v>-0.1234999999999999</v>
@@ -2317,7 +2317,7 @@
         <v>5.1393</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.5252</v>
+        <v>-6.525200000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.3129</v>
@@ -2326,16 +2326,16 @@
         <v>9.787499999999998</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.752600000000001</v>
+        <v>-4.7528</v>
       </c>
       <c r="T24" t="n">
         <v>-4.7767</v>
       </c>
       <c r="U24" t="n">
-        <v>0.02400000000000002</v>
+        <v>0.02389999999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>-6.759199999999999</v>
+        <v>-6.7592</v>
       </c>
       <c r="W24" t="n">
         <v>7.0371</v>
